--- a/08-投资跟踪/AH股投资标的/AH股投资标的_跟踪2.0.xlsx
+++ b/08-投资跟踪/AH股投资标的/AH股投资标的_跟踪2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="126">
   <si>
     <t>分类</t>
   </si>
@@ -161,99 +161,6 @@
   </si>
   <si>
     <t>行业ETF</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>9988</t>
-  </si>
-  <si>
-    <t>9992</t>
-  </si>
-  <si>
-    <t>9896</t>
-  </si>
-  <si>
-    <t>291</t>
-  </si>
-  <si>
-    <t>921</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>600048</t>
-  </si>
-  <si>
-    <t>06049</t>
-  </si>
-  <si>
-    <t>2669</t>
-  </si>
-  <si>
-    <t>000786</t>
-  </si>
-  <si>
-    <t>881</t>
-  </si>
-  <si>
-    <t>0763</t>
-  </si>
-  <si>
-    <t>1193</t>
-  </si>
-  <si>
-    <t>600315</t>
-  </si>
-  <si>
-    <t>2367</t>
-  </si>
-  <si>
-    <t>3320</t>
-  </si>
-  <si>
-    <t>300003</t>
-  </si>
-  <si>
-    <t>300294</t>
-  </si>
-  <si>
-    <t>300119</t>
-  </si>
-  <si>
-    <t>002709</t>
-  </si>
-  <si>
-    <t>688396</t>
-  </si>
-  <si>
-    <t>603697</t>
-  </si>
-  <si>
-    <t>600887</t>
-  </si>
-  <si>
-    <t>600754</t>
-  </si>
-  <si>
-    <t>601061</t>
-  </si>
-  <si>
-    <t>159995</t>
-  </si>
-  <si>
-    <t>515450</t>
-  </si>
-  <si>
-    <t>516020</t>
-  </si>
-  <si>
-    <t>159796</t>
-  </si>
-  <si>
-    <t>513120</t>
   </si>
   <si>
     <t>腾讯控股</t>
@@ -491,16 +398,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -516,7 +415,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -524,30 +423,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,91 +727,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -938,17 +819,17 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>700</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="D2" t="s">
-        <v>111</v>
-      </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F2">
         <v>40.5</v>
@@ -981,13 +862,13 @@
         <v>6.8</v>
       </c>
       <c r="P2" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="Q2" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R2" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S2">
         <v>14</v>
@@ -996,13 +877,13 @@
         <v>32.8</v>
       </c>
       <c r="U2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V2" t="s">
         <v>124</v>
       </c>
-      <c r="V2" t="s">
-        <v>155</v>
-      </c>
       <c r="W2" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X2">
         <v>524</v>
@@ -1020,24 +901,24 @@
         <v>1.25</v>
       </c>
       <c r="AC2" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>9988</v>
+      </c>
+      <c r="C3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F3">
         <v>43.8</v>
@@ -1070,13 +951,13 @@
         <v>5.9</v>
       </c>
       <c r="P3" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="R3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S3">
         <v>13.3</v>
@@ -1085,13 +966,13 @@
         <v>30.7</v>
       </c>
       <c r="U3" t="s">
+        <v>94</v>
+      </c>
+      <c r="V3" t="s">
+        <v>124</v>
+      </c>
+      <c r="W3" t="s">
         <v>125</v>
-      </c>
-      <c r="V3" t="s">
-        <v>155</v>
-      </c>
-      <c r="W3" t="s">
-        <v>156</v>
       </c>
       <c r="X3">
         <v>148.4</v>
@@ -1109,24 +990,24 @@
         <v>1.25</v>
       </c>
       <c r="AC3" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>9992</v>
+      </c>
+      <c r="C4" t="s">
         <v>51</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" t="s">
         <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" t="s">
-        <v>113</v>
       </c>
       <c r="F4">
         <v>56.1</v>
@@ -1159,13 +1040,13 @@
         <v>7.7</v>
       </c>
       <c r="P4" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q4" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="R4" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S4">
         <v>14</v>
@@ -1174,13 +1055,13 @@
         <v>32.9</v>
       </c>
       <c r="U4" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="V4" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W4" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X4">
         <v>232</v>
@@ -1198,24 +1079,24 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:29">
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>9896</v>
+      </c>
+      <c r="C5" t="s">
         <v>52</v>
       </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="F5">
         <v>58.8</v>
@@ -1248,13 +1129,13 @@
         <v>7.1</v>
       </c>
       <c r="P5" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q5" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="R5" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S5">
         <v>5.3</v>
@@ -1263,13 +1144,13 @@
         <v>22.5</v>
       </c>
       <c r="U5" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="V5" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W5" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X5">
         <v>38.2</v>
@@ -1287,24 +1168,24 @@
         <v>1.25</v>
       </c>
       <c r="AC5" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:29">
       <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>291</v>
+      </c>
+      <c r="C6" t="s">
         <v>53</v>
       </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F6">
         <v>54.9</v>
@@ -1337,13 +1218,13 @@
         <v>10</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="Q6" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R6" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S6">
         <v>14</v>
@@ -1352,13 +1233,13 @@
         <v>34.4</v>
       </c>
       <c r="U6" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="V6" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W6" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X6">
         <v>27.42</v>
@@ -1376,24 +1257,24 @@
         <v>1.25</v>
       </c>
       <c r="AC6" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:29">
       <c r="A7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>921</v>
+      </c>
+      <c r="C7" t="s">
         <v>54</v>
       </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F7">
         <v>53.4</v>
@@ -1426,13 +1307,13 @@
         <v>6.5</v>
       </c>
       <c r="P7" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q7" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R7" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1441,13 +1322,13 @@
         <v>27.4</v>
       </c>
       <c r="U7" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="V7" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W7" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X7">
         <v>24.04</v>
@@ -1465,24 +1346,24 @@
         <v>1.25</v>
       </c>
       <c r="AC7" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>1610</v>
+      </c>
+      <c r="C8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>50.1</v>
@@ -1515,13 +1396,13 @@
         <v>6.7</v>
       </c>
       <c r="P8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="R8" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S8">
         <v>16</v>
@@ -1530,13 +1411,13 @@
         <v>34.4</v>
       </c>
       <c r="U8" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="V8" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W8" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X8">
         <v>1.56</v>
@@ -1554,24 +1435,24 @@
         <v>1.25</v>
       </c>
       <c r="AC8" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:29">
       <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>600048</v>
+      </c>
+      <c r="C9" t="s">
         <v>56</v>
       </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="F9">
         <v>57.6</v>
@@ -1604,13 +1485,13 @@
         <v>7.6</v>
       </c>
       <c r="P9" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R9" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="S9">
         <v>6.7</v>
@@ -1619,13 +1500,13 @@
         <v>24.8</v>
       </c>
       <c r="U9" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="V9" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W9" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X9">
         <v>6.96</v>
@@ -1643,24 +1524,24 @@
         <v>1.25</v>
       </c>
       <c r="AC9" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:29">
       <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>6049</v>
+      </c>
+      <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F10">
         <v>50.9</v>
@@ -1693,13 +1574,13 @@
         <v>9.6</v>
       </c>
       <c r="P10" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="R10" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S10">
         <v>14</v>
@@ -1708,13 +1589,13 @@
         <v>34.1</v>
       </c>
       <c r="U10" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="V10" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W10" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X10">
         <v>32.4</v>
@@ -1732,24 +1613,24 @@
         <v>1.25</v>
       </c>
       <c r="AC10" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:29">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>2669</v>
+      </c>
+      <c r="C11" t="s">
         <v>58</v>
       </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>56.3</v>
@@ -1782,13 +1663,13 @@
         <v>7.1</v>
       </c>
       <c r="P11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q11" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="R11" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S11">
         <v>11.3</v>
@@ -1797,13 +1678,13 @@
         <v>30.2</v>
       </c>
       <c r="U11" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="V11" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W11" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X11">
         <v>4.33</v>
@@ -1821,24 +1702,24 @@
         <v>1.25</v>
       </c>
       <c r="AC11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:29">
       <c r="A12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>786</v>
+      </c>
+      <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F12">
         <v>42.5</v>
@@ -1871,13 +1752,13 @@
         <v>6.1</v>
       </c>
       <c r="P12" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="R12" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S12">
         <v>16</v>
@@ -1886,13 +1767,13 @@
         <v>32.8</v>
       </c>
       <c r="U12" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="V12" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W12" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X12">
         <v>28.68</v>
@@ -1910,24 +1791,24 @@
         <v>1.25</v>
       </c>
       <c r="AC12" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:29">
       <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>881</v>
+      </c>
+      <c r="C13" t="s">
         <v>60</v>
       </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F13">
         <v>40.8</v>
@@ -1960,13 +1841,13 @@
         <v>7.6</v>
       </c>
       <c r="P13" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q13" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R13" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S13">
         <v>9.300000000000001</v>
@@ -1975,13 +1856,13 @@
         <v>29.1</v>
       </c>
       <c r="U13" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="V13" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W13" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X13">
         <v>11.61</v>
@@ -1999,24 +1880,24 @@
         <v>1.25</v>
       </c>
       <c r="AC13" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:29">
       <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14">
+        <v>763</v>
+      </c>
+      <c r="C14" t="s">
         <v>61</v>
       </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="F14">
         <v>47.1</v>
@@ -2049,13 +1930,13 @@
         <v>6.6</v>
       </c>
       <c r="P14" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q14" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="R14" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S14">
         <v>12</v>
@@ -2064,13 +1945,13 @@
         <v>29.1</v>
       </c>
       <c r="U14" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="V14" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W14" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X14">
         <v>27.4</v>
@@ -2088,24 +1969,24 @@
         <v>1.25</v>
       </c>
       <c r="AC14" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:29">
       <c r="A15" t="s">
         <v>37</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>1193</v>
+      </c>
+      <c r="C15" t="s">
         <v>62</v>
       </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F15">
         <v>56.4</v>
@@ -2138,13 +2019,13 @@
         <v>7.3</v>
       </c>
       <c r="P15" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q15" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="R15" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S15">
         <v>7.3</v>
@@ -2153,13 +2034,13 @@
         <v>25.2</v>
       </c>
       <c r="U15" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="V15" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W15" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X15">
         <v>21.24</v>
@@ -2177,24 +2058,24 @@
         <v>1.25</v>
       </c>
       <c r="AC15" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:29">
       <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>600315</v>
+      </c>
+      <c r="C16" t="s">
         <v>63</v>
       </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F16">
         <v>48.7</v>
@@ -2227,13 +2108,13 @@
         <v>9</v>
       </c>
       <c r="P16" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q16" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="R16" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S16">
         <v>11.3</v>
@@ -2242,13 +2123,13 @@
         <v>31</v>
       </c>
       <c r="U16" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="V16" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W16" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X16">
         <v>21.63</v>
@@ -2266,24 +2147,24 @@
         <v>1.25</v>
       </c>
       <c r="AC16" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:29">
       <c r="A17" t="s">
         <v>38</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>2367</v>
+      </c>
+      <c r="C17" t="s">
         <v>64</v>
       </c>
-      <c r="C17" t="s">
-        <v>95</v>
-      </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F17">
         <v>49.5</v>
@@ -2316,13 +2197,13 @@
         <v>8</v>
       </c>
       <c r="P17" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R17" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S17">
         <v>7.3</v>
@@ -2331,13 +2212,13 @@
         <v>27.3</v>
       </c>
       <c r="U17" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="V17" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W17" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X17">
         <v>31.96</v>
@@ -2355,24 +2236,24 @@
         <v>1.25</v>
       </c>
       <c r="AC17" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:29">
       <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>3320</v>
+      </c>
+      <c r="C18" t="s">
         <v>65</v>
       </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F18">
         <v>48.5</v>
@@ -2405,13 +2286,13 @@
         <v>7.3</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q18" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R18" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S18">
         <v>9.300000000000001</v>
@@ -2420,13 +2301,13 @@
         <v>28</v>
       </c>
       <c r="U18" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="V18" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W18" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X18">
         <v>4.69</v>
@@ -2444,24 +2325,24 @@
         <v>1.25</v>
       </c>
       <c r="AC18" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:29">
       <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>300003</v>
+      </c>
+      <c r="C19" t="s">
         <v>66</v>
       </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F19">
         <v>54.3</v>
@@ -2494,13 +2375,13 @@
         <v>6.9</v>
       </c>
       <c r="P19" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q19" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="R19" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="S19">
         <v>10.7</v>
@@ -2509,13 +2390,13 @@
         <v>28.6</v>
       </c>
       <c r="U19" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="V19" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W19" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X19">
         <v>18.33</v>
@@ -2533,24 +2414,24 @@
         <v>1.25</v>
       </c>
       <c r="AC19" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:29">
       <c r="A20" t="s">
         <v>41</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20">
+        <v>300294</v>
+      </c>
+      <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F20">
         <v>48.9</v>
@@ -2583,13 +2464,13 @@
         <v>7.4</v>
       </c>
       <c r="P20" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q20" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R20" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="S20">
         <v>6.7</v>
@@ -2598,13 +2479,13 @@
         <v>24.6</v>
       </c>
       <c r="U20" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="V20" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W20" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X20">
         <v>22.3</v>
@@ -2622,24 +2503,24 @@
         <v>1.25</v>
       </c>
       <c r="AC20" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:29">
       <c r="A21" t="s">
         <v>42</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>300119</v>
+      </c>
+      <c r="C21" t="s">
         <v>68</v>
       </c>
-      <c r="C21" t="s">
-        <v>99</v>
-      </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F21">
         <v>55.5</v>
@@ -2672,13 +2553,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q21" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R21" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="S21">
         <v>4.7</v>
@@ -2687,13 +2568,13 @@
         <v>23</v>
       </c>
       <c r="U21" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="V21" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W21" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X21">
         <v>19.54</v>
@@ -2711,24 +2592,24 @@
         <v>1.25</v>
       </c>
       <c r="AC21" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:29">
       <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22">
+        <v>2709</v>
+      </c>
+      <c r="C22" t="s">
         <v>69</v>
       </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F22">
         <v>43.6</v>
@@ -2761,13 +2642,13 @@
         <v>6.7</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q22" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R22" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S22">
         <v>7.3</v>
@@ -2776,13 +2657,13 @@
         <v>24.4</v>
       </c>
       <c r="U22" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="V22" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W22" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X22">
         <v>44</v>
@@ -2800,24 +2681,24 @@
         <v>1.25</v>
       </c>
       <c r="AC22" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:29">
       <c r="A23" t="s">
         <v>44</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23">
+        <v>688396</v>
+      </c>
+      <c r="C23" t="s">
         <v>70</v>
       </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="F23">
         <v>57.8</v>
@@ -2850,13 +2731,13 @@
         <v>9.699999999999999</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q23" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="R23" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S23">
         <v>11.3</v>
@@ -2865,13 +2746,13 @@
         <v>32.7</v>
       </c>
       <c r="U23" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="V23" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W23" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X23">
         <v>59.81</v>
@@ -2889,24 +2770,24 @@
         <v>1.25</v>
       </c>
       <c r="AC23" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:29">
       <c r="A24" t="s">
         <v>45</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24">
+        <v>603697</v>
+      </c>
+      <c r="C24" t="s">
         <v>71</v>
       </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F24">
         <v>50.9</v>
@@ -2939,13 +2820,13 @@
         <v>9.1</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q24" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R24" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S24">
         <v>9.300000000000001</v>
@@ -2954,13 +2835,13 @@
         <v>30.3</v>
       </c>
       <c r="U24" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="V24" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W24" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X24">
         <v>12.43</v>
@@ -2978,24 +2859,24 @@
         <v>1.25</v>
       </c>
       <c r="AC24" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:29">
       <c r="A25" t="s">
         <v>45</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25">
+        <v>600887</v>
+      </c>
+      <c r="C25" t="s">
         <v>72</v>
       </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F25">
         <v>45.4</v>
@@ -3028,13 +2909,13 @@
         <v>5.3</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q25" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R25" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="S25">
         <v>4.7</v>
@@ -3043,13 +2924,13 @@
         <v>21.9</v>
       </c>
       <c r="U25" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="V25" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W25" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X25">
         <v>26.3</v>
@@ -3067,24 +2948,24 @@
         <v>1.25</v>
       </c>
       <c r="AC25" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:29">
       <c r="A26" t="s">
         <v>46</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26">
+        <v>600754</v>
+      </c>
+      <c r="C26" t="s">
         <v>73</v>
       </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F26">
         <v>50.6</v>
@@ -3117,13 +2998,13 @@
         <v>8.6</v>
       </c>
       <c r="P26" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q26" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R26" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S26">
         <v>10</v>
@@ -3132,13 +3013,13 @@
         <v>30.2</v>
       </c>
       <c r="U26" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="V26" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W26" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X26">
         <v>27.37</v>
@@ -3156,24 +3037,24 @@
         <v>1.25</v>
       </c>
       <c r="AC26" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:29">
       <c r="A27" t="s">
         <v>47</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27">
+        <v>601061</v>
+      </c>
+      <c r="C27" t="s">
         <v>74</v>
       </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F27">
         <v>50.5</v>
@@ -3206,13 +3087,13 @@
         <v>6.6</v>
       </c>
       <c r="P27" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q27" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="R27" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -3221,13 +3102,13 @@
         <v>25.4</v>
       </c>
       <c r="U27" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="V27" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W27" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X27">
         <v>15.14</v>
@@ -3245,24 +3126,24 @@
         <v>1.25</v>
       </c>
       <c r="AC27" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:29">
       <c r="A28" t="s">
         <v>48</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28">
+        <v>159995</v>
+      </c>
+      <c r="C28" t="s">
         <v>75</v>
       </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F28">
         <v>52.7</v>
@@ -3295,13 +3176,13 @@
         <v>6.9</v>
       </c>
       <c r="P28" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q28" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R28" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S28">
         <v>9.300000000000001</v>
@@ -3310,13 +3191,13 @@
         <v>26.6</v>
       </c>
       <c r="U28" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="V28" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W28" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X28">
         <v>1.95</v>
@@ -3334,24 +3215,24 @@
         <v>1.25</v>
       </c>
       <c r="AC28" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:29">
       <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29">
+        <v>515450</v>
+      </c>
+      <c r="C29" t="s">
         <v>76</v>
       </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F29">
         <v>53.5</v>
@@ -3384,13 +3265,13 @@
         <v>7.1</v>
       </c>
       <c r="P29" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q29" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R29" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -3399,13 +3280,13 @@
         <v>29.1</v>
       </c>
       <c r="U29" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="V29" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W29" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X29">
         <v>1.41</v>
@@ -3423,24 +3304,24 @@
         <v>1.25</v>
       </c>
       <c r="AC29" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:29">
       <c r="A30" t="s">
         <v>48</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30">
+        <v>516020</v>
+      </c>
+      <c r="C30" t="s">
         <v>77</v>
       </c>
-      <c r="C30" t="s">
-        <v>108</v>
-      </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="F30">
         <v>54.5</v>
@@ -3473,13 +3354,13 @@
         <v>8.300000000000001</v>
       </c>
       <c r="P30" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q30" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R30" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="S30">
         <v>9.300000000000001</v>
@@ -3488,13 +3369,13 @@
         <v>29.3</v>
       </c>
       <c r="U30" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="V30" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W30" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -3512,24 +3393,24 @@
         <v>1.25</v>
       </c>
       <c r="AC30" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:29">
       <c r="A31" t="s">
         <v>48</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31">
+        <v>159796</v>
+      </c>
+      <c r="C31" t="s">
         <v>78</v>
       </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F31">
         <v>43.8</v>
@@ -3562,13 +3443,13 @@
         <v>9.1</v>
       </c>
       <c r="P31" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="Q31" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R31" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S31">
         <v>10</v>
@@ -3577,13 +3458,13 @@
         <v>30.2</v>
       </c>
       <c r="U31" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="V31" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W31" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X31">
         <v>1</v>
@@ -3601,24 +3482,24 @@
         <v>1.25</v>
       </c>
       <c r="AC31" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:29">
       <c r="A32" t="s">
         <v>48</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32">
+        <v>513120</v>
+      </c>
+      <c r="C32" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
-        <v>110</v>
-      </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="F32">
         <v>46.8</v>
@@ -3651,13 +3532,13 @@
         <v>6.8</v>
       </c>
       <c r="P32" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="Q32" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="R32" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="S32">
         <v>6.7</v>
@@ -3666,13 +3547,13 @@
         <v>25.1</v>
       </c>
       <c r="U32" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="V32" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="W32" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="X32">
         <v>1.28</v>
@@ -3690,7 +3571,7 @@
         <v>1.25</v>
       </c>
       <c r="AC32" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
